--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/17,08,26 Останкино КИ и ЗПФ/машина САП 23,08 Донецк_Малахутин_ПРС КИ/Заказ ЛП Малахутин 23,08.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/17,08,26 Останкино КИ и ЗПФ/машина САП 23,08 Донецк_Малахутин_ПРС КИ/Заказ ЛП Малахутин 23,08.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\машина САП 23,08 Донецк_Малахутин_ПРС КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\17,08,26 Останкино КИ и ЗПФ\машина САП 23,08 Донецк_Малахутин_ПРС КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA8CA50-40DD-446A-ABA7-6799AA54E5EB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962A28A2-AE4F-4186-ABEC-877E9D1C2CC5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6262,7 +6262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BO1692"/>
@@ -6488,7 +6488,7 @@
       <c r="BN9" s="120"/>
       <c r="BO9" s="120"/>
     </row>
-    <row r="10" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48"/>
       <c r="B10" s="43" t="s">
         <v>18</v>
@@ -6502,7 +6502,7 @@
       <c r="I10" s="43"/>
       <c r="J10" s="44"/>
     </row>
-    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58">
         <v>4561</v>
       </c>
@@ -6588,7 +6588,7 @@
       <c r="BN11" s="121"/>
       <c r="BO11" s="121"/>
     </row>
-    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="145">
         <v>7536</v>
       </c>
@@ -6676,7 +6676,7 @@
       <c r="BN12" s="121"/>
       <c r="BO12" s="121"/>
     </row>
-    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58">
         <v>3215</v>
       </c>
@@ -7074,7 +7074,7 @@
       <c r="J18" s="61"/>
       <c r="L18" s="122"/>
     </row>
-    <row r="19" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58">
         <v>6861</v>
       </c>
@@ -7104,7 +7104,7 @@
       <c r="J19" s="29"/>
       <c r="L19" s="122"/>
     </row>
-    <row r="20" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="58">
         <v>6862</v>
       </c>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="L21" s="122"/>
     </row>
-    <row r="22" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="58">
         <v>7334</v>
       </c>
@@ -7230,7 +7230,7 @@
       <c r="J23" s="29"/>
       <c r="L23" s="122"/>
     </row>
-    <row r="24" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58">
         <v>8014</v>
       </c>
@@ -7494,7 +7494,7 @@
       <c r="BN26" s="122"/>
       <c r="BO26" s="122"/>
     </row>
-    <row r="27" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="147">
         <v>6340</v>
       </c>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L27" s="122"/>
     </row>
-    <row r="28" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="147">
         <v>6341</v>
       </c>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L28" s="122"/>
     </row>
-    <row r="29" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="58">
         <v>6333</v>
       </c>
@@ -7620,7 +7620,7 @@
       <c r="J30" s="29"/>
       <c r="L30" s="122"/>
     </row>
-    <row r="31" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="58">
         <v>7343</v>
       </c>
@@ -7738,7 +7738,7 @@
       <c r="BN32" s="122"/>
       <c r="BO32" s="122"/>
     </row>
-    <row r="33" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="58">
         <v>7231</v>
       </c>
@@ -7824,7 +7824,7 @@
       <c r="BN33" s="122"/>
       <c r="BO33" s="122"/>
     </row>
-    <row r="34" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="48" t="s">
         <v>104</v>
       </c>
@@ -7841,7 +7841,7 @@
       <c r="J34" s="44"/>
       <c r="L34" s="122"/>
     </row>
-    <row r="35" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58">
         <v>6767</v>
       </c>
@@ -7927,7 +7927,7 @@
       <c r="BN35" s="122"/>
       <c r="BO35" s="122"/>
     </row>
-    <row r="36" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="58">
         <v>6761</v>
       </c>
@@ -8013,7 +8013,7 @@
       <c r="BN36" s="122"/>
       <c r="BO36" s="122"/>
     </row>
-    <row r="37" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="58">
         <v>6764</v>
       </c>
@@ -8099,7 +8099,7 @@
       <c r="BN37" s="122"/>
       <c r="BO37" s="122"/>
     </row>
-    <row r="38" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="58">
         <v>6254</v>
       </c>
@@ -8185,7 +8185,7 @@
       <c r="BN38" s="122"/>
       <c r="BO38" s="122"/>
     </row>
-    <row r="39" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="58">
         <v>7075</v>
       </c>
@@ -8535,7 +8535,7 @@
       <c r="BN42" s="122"/>
       <c r="BO42" s="122"/>
     </row>
-    <row r="43" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="58">
         <v>7076</v>
       </c>
@@ -8797,7 +8797,7 @@
       <c r="BN45" s="122"/>
       <c r="BO45" s="122"/>
     </row>
-    <row r="46" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="58">
         <v>6661</v>
       </c>
@@ -8883,7 +8883,7 @@
       <c r="BN46" s="122"/>
       <c r="BO46" s="122"/>
     </row>
-    <row r="47" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="58">
         <v>6759</v>
       </c>
@@ -9145,7 +9145,7 @@
       <c r="BN49" s="122"/>
       <c r="BO49" s="122"/>
     </row>
-    <row r="50" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="58">
         <v>7074</v>
       </c>
@@ -9231,7 +9231,7 @@
       <c r="BN50" s="122"/>
       <c r="BO50" s="122"/>
     </row>
-    <row r="51" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="58">
         <v>7123</v>
       </c>
@@ -9317,7 +9317,7 @@
       <c r="BN51" s="122"/>
       <c r="BO51" s="122"/>
     </row>
-    <row r="52" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="58">
         <v>5819</v>
       </c>
@@ -9403,7 +9403,7 @@
       <c r="BN52" s="122"/>
       <c r="BO52" s="122"/>
     </row>
-    <row r="53" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="58">
         <v>6475</v>
       </c>
@@ -9489,7 +9489,7 @@
       <c r="BN53" s="122"/>
       <c r="BO53" s="122"/>
     </row>
-    <row r="54" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="147">
         <v>7284</v>
       </c>
@@ -9667,7 +9667,7 @@
       <c r="BN55" s="122"/>
       <c r="BO55" s="122"/>
     </row>
-    <row r="56" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="58">
         <v>7601</v>
       </c>
@@ -9753,7 +9753,7 @@
       <c r="BN56" s="122"/>
       <c r="BO56" s="122"/>
     </row>
-    <row r="57" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="147">
         <v>7371</v>
       </c>
@@ -9841,7 +9841,7 @@
       <c r="BN57" s="122"/>
       <c r="BO57" s="122"/>
     </row>
-    <row r="58" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="58">
         <v>6837</v>
       </c>
@@ -9927,7 +9927,7 @@
       <c r="BN58" s="122"/>
       <c r="BO58" s="122"/>
     </row>
-    <row r="59" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="58">
         <v>7080</v>
       </c>
@@ -9957,7 +9957,7 @@
       <c r="J59" s="29"/>
       <c r="L59" s="122"/>
     </row>
-    <row r="60" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="58">
         <v>6724</v>
       </c>
@@ -10019,7 +10019,7 @@
       <c r="J61" s="29"/>
       <c r="L61" s="122"/>
     </row>
-    <row r="62" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="58">
         <v>6713</v>
       </c>
@@ -10081,7 +10081,7 @@
       <c r="J63" s="29"/>
       <c r="L63" s="122"/>
     </row>
-    <row r="64" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="58">
         <v>6602</v>
       </c>
@@ -10111,7 +10111,7 @@
       <c r="J64" s="29"/>
       <c r="L64" s="122"/>
     </row>
-    <row r="65" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="145">
         <v>7040</v>
       </c>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="L65" s="122"/>
     </row>
-    <row r="66" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="145">
         <v>7521</v>
       </c>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="L66" s="122"/>
     </row>
-    <row r="67" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="58">
         <v>7073</v>
       </c>
@@ -10205,7 +10205,7 @@
       <c r="J67" s="29"/>
       <c r="L67" s="122"/>
     </row>
-    <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="58">
         <v>7276</v>
       </c>
@@ -10235,7 +10235,7 @@
       <c r="J68" s="29"/>
       <c r="L68" s="122"/>
     </row>
-    <row r="69" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="58">
         <v>6616</v>
       </c>
@@ -10265,7 +10265,7 @@
       <c r="J69" s="29"/>
       <c r="L69" s="122"/>
     </row>
-    <row r="70" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="58">
         <v>7044</v>
       </c>
@@ -10295,7 +10295,7 @@
       <c r="J70" s="29"/>
       <c r="L70" s="122"/>
     </row>
-    <row r="71" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="147">
         <v>7385</v>
       </c>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="L71" s="122"/>
     </row>
-    <row r="72" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="147">
         <v>7460</v>
       </c>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="L72" s="122"/>
     </row>
-    <row r="73" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="48" t="s">
         <v>104</v>
       </c>
@@ -10376,7 +10376,7 @@
       <c r="J73" s="44"/>
       <c r="L73" s="122"/>
     </row>
-    <row r="74" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A74" s="58">
         <v>6527</v>
       </c>
@@ -10406,7 +10406,7 @@
       <c r="J74" s="61"/>
       <c r="L74" s="122"/>
     </row>
-    <row r="75" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="58">
         <v>6550</v>
       </c>
@@ -10468,7 +10468,7 @@
       <c r="J76" s="29"/>
       <c r="L76" s="122"/>
     </row>
-    <row r="77" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="58">
         <v>7001</v>
       </c>
@@ -10562,7 +10562,7 @@
       <c r="J79" s="29"/>
       <c r="L79" s="122"/>
     </row>
-    <row r="80" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="58">
         <v>6609</v>
       </c>
@@ -10592,7 +10592,7 @@
       <c r="J80" s="29"/>
       <c r="L80" s="122"/>
     </row>
-    <row r="81" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="48" t="s">
         <v>104</v>
       </c>
@@ -10609,7 +10609,7 @@
       <c r="J81" s="44"/>
       <c r="L81" s="122"/>
     </row>
-    <row r="82" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A82" s="145">
         <v>7564</v>
       </c>
@@ -10641,7 +10641,7 @@
       </c>
       <c r="L82" s="122"/>
     </row>
-    <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="58">
         <v>7133</v>
       </c>
@@ -10671,7 +10671,7 @@
       <c r="J83" s="61"/>
       <c r="L83" s="122"/>
     </row>
-    <row r="84" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="58">
         <v>6946</v>
       </c>
@@ -10701,7 +10701,7 @@
       <c r="J84" s="29"/>
       <c r="L84" s="122"/>
     </row>
-    <row r="85" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="58">
         <v>7132</v>
       </c>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="L90" s="122"/>
     </row>
-    <row r="91" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="145">
         <v>7489</v>
       </c>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="L91" s="122"/>
     </row>
-    <row r="92" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="58">
         <v>6807</v>
       </c>
@@ -10955,7 +10955,7 @@
       <c r="J92" s="29"/>
       <c r="L92" s="122"/>
     </row>
-    <row r="93" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="58">
         <v>6787</v>
       </c>
@@ -11017,7 +11017,7 @@
       <c r="J94" s="61"/>
       <c r="L94" s="122"/>
     </row>
-    <row r="95" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="58">
         <v>7169</v>
       </c>
@@ -11047,7 +11047,7 @@
       <c r="J95" s="29"/>
       <c r="L95" s="122"/>
     </row>
-    <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="58">
         <v>7233</v>
       </c>
@@ -11109,7 +11109,7 @@
       <c r="J97" s="50"/>
       <c r="L97" s="122"/>
     </row>
-    <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="58">
         <v>7177</v>
       </c>
@@ -11203,7 +11203,7 @@
       <c r="J100" s="50"/>
       <c r="L100" s="122"/>
     </row>
-    <row r="101" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="58">
         <v>7238</v>
       </c>
@@ -11233,7 +11233,7 @@
       <c r="J101" s="50"/>
       <c r="L101" s="122"/>
     </row>
-    <row r="102" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="147">
         <v>7237</v>
       </c>
@@ -11297,7 +11297,7 @@
       <c r="J103" s="50"/>
       <c r="L103" s="122"/>
     </row>
-    <row r="104" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="58">
         <v>7332</v>
       </c>
@@ -11359,7 +11359,7 @@
       <c r="J105" s="50"/>
       <c r="L105" s="122"/>
     </row>
-    <row r="106" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="145">
         <v>7608</v>
       </c>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="L106" s="122"/>
     </row>
-    <row r="107" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:67" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="145">
         <v>7610</v>
       </c>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="L107" s="122"/>
     </row>
-    <row r="108" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="48" t="s">
         <v>104</v>
       </c>
@@ -11496,7 +11496,7 @@
       <c r="BN108" s="122"/>
       <c r="BO108" s="122"/>
     </row>
-    <row r="109" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A109" s="58">
         <v>614</v>
       </c>
@@ -11582,7 +11582,7 @@
       <c r="BN109" s="122"/>
       <c r="BO109" s="122"/>
     </row>
-    <row r="110" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="58">
         <v>3287</v>
       </c>
@@ -11668,7 +11668,7 @@
       <c r="BN110" s="122"/>
       <c r="BO110" s="122"/>
     </row>
-    <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="58">
         <v>5708</v>
       </c>
@@ -11698,7 +11698,7 @@
       <c r="J111" s="29"/>
       <c r="L111" s="122"/>
     </row>
-    <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="58">
         <v>4117</v>
       </c>
@@ -11728,7 +11728,7 @@
       <c r="J112" s="29"/>
       <c r="L112" s="122"/>
     </row>
-    <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="58">
         <v>7316</v>
       </c>
@@ -11758,7 +11758,7 @@
       <c r="J113" s="29"/>
       <c r="L113" s="122"/>
     </row>
-    <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="58">
         <v>7317</v>
       </c>
@@ -11788,7 +11788,7 @@
       <c r="J114" s="29"/>
       <c r="L114" s="122"/>
     </row>
-    <row r="115" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="58">
         <v>7143</v>
       </c>
@@ -11818,7 +11818,7 @@
       <c r="J115" s="29"/>
       <c r="L115" s="122"/>
     </row>
-    <row r="116" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="58">
         <v>7147</v>
       </c>
@@ -11848,7 +11848,7 @@
       <c r="J116" s="29"/>
       <c r="L116" s="122"/>
     </row>
-    <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="58">
         <v>7456</v>
       </c>
@@ -11878,7 +11878,7 @@
       <c r="J117" s="29"/>
       <c r="L117" s="122"/>
     </row>
-    <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="58">
         <v>7318</v>
       </c>
@@ -11940,7 +11940,7 @@
       <c r="J119" s="61"/>
       <c r="L119" s="122"/>
     </row>
-    <row r="120" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="58">
         <v>7364</v>
       </c>
@@ -11970,7 +11970,7 @@
       <c r="J120" s="29"/>
       <c r="L120" s="122"/>
     </row>
-    <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="58">
         <v>7383</v>
       </c>
@@ -12000,7 +12000,7 @@
       <c r="J121" s="29"/>
       <c r="L121" s="122"/>
     </row>
-    <row r="122" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="58">
         <v>6967</v>
       </c>
@@ -12030,7 +12030,7 @@
       <c r="J122" s="29"/>
       <c r="L122" s="122"/>
     </row>
-    <row r="123" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="58">
         <v>4993</v>
       </c>
@@ -12060,7 +12060,7 @@
       <c r="J123" s="29"/>
       <c r="L123" s="122"/>
     </row>
-    <row r="124" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="58">
         <v>6937</v>
       </c>
@@ -12154,7 +12154,7 @@
       <c r="J126" s="61"/>
       <c r="L126" s="122"/>
     </row>
-    <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="58">
         <v>6832</v>
       </c>
@@ -12184,7 +12184,7 @@
       <c r="J127" s="29"/>
       <c r="L127" s="122"/>
     </row>
-    <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="58">
         <v>7299</v>
       </c>
@@ -12214,7 +12214,7 @@
       <c r="J128" s="29"/>
       <c r="L128" s="122"/>
     </row>
-    <row r="129" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="58">
         <v>7386</v>
       </c>
@@ -12244,7 +12244,7 @@
       <c r="J129" s="29"/>
       <c r="L129" s="122"/>
     </row>
-    <row r="130" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="58">
         <v>5679</v>
       </c>
@@ -12370,7 +12370,7 @@
       <c r="J133" s="61"/>
       <c r="L133" s="122"/>
     </row>
-    <row r="134" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="58">
         <v>6221</v>
       </c>
@@ -12400,7 +12400,7 @@
       <c r="J134" s="29"/>
       <c r="L134" s="122"/>
     </row>
-    <row r="135" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="58">
         <v>6222</v>
       </c>
@@ -12430,7 +12430,7 @@
       <c r="J135" s="29"/>
       <c r="L135" s="122"/>
     </row>
-    <row r="136" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="147">
         <v>6834</v>
       </c>
@@ -12462,7 +12462,7 @@
       </c>
       <c r="L136" s="122"/>
     </row>
-    <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="147">
         <v>6965</v>
       </c>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="L137" s="122"/>
     </row>
-    <row r="138" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="147">
         <v>6557</v>
       </c>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="L138" s="122"/>
     </row>
-    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A139" s="145">
         <v>7626</v>
       </c>
@@ -12558,7 +12558,7 @@
       </c>
       <c r="L139" s="122"/>
     </row>
-    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="48" t="s">
         <v>104</v>
       </c>
@@ -12575,7 +12575,7 @@
       <c r="J140" s="44"/>
       <c r="L140" s="122"/>
     </row>
-    <row r="141" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:67" ht="16.149999999999999" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A141" s="58">
         <v>6470</v>
       </c>
@@ -12605,7 +12605,7 @@
       <c r="J141" s="29"/>
       <c r="L141" s="122"/>
     </row>
-    <row r="142" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="58">
         <v>6495</v>
       </c>
@@ -12781,7 +12781,7 @@
       <c r="BN143" s="122"/>
       <c r="BO143" s="122"/>
     </row>
-    <row r="144" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="58">
         <v>6866</v>
       </c>
@@ -12867,7 +12867,7 @@
       <c r="BN144" s="122"/>
       <c r="BO144" s="122"/>
     </row>
-    <row r="145" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="58">
         <v>6025</v>
       </c>
@@ -12953,7 +12953,7 @@
       <c r="BN145" s="122"/>
       <c r="BO145" s="122"/>
     </row>
-    <row r="146" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="58">
         <v>4584</v>
       </c>
@@ -13129,7 +13129,7 @@
       <c r="BN147" s="122"/>
       <c r="BO147" s="122"/>
     </row>
-    <row r="148" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="58">
         <v>5495</v>
       </c>
@@ -13215,7 +13215,7 @@
       <c r="BN148" s="122"/>
       <c r="BO148" s="122"/>
     </row>
-    <row r="149" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="58">
         <v>7377</v>
       </c>
@@ -13301,7 +13301,7 @@
       <c r="BN149" s="122"/>
       <c r="BO149" s="122"/>
     </row>
-    <row r="150" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="58">
         <v>6925</v>
       </c>
@@ -13387,7 +13387,7 @@
       <c r="BN150" s="122"/>
       <c r="BO150" s="122"/>
     </row>
-    <row r="151" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="145">
         <v>7647</v>
       </c>
@@ -13475,7 +13475,7 @@
       <c r="BN151" s="122"/>
       <c r="BO151" s="122"/>
     </row>
-    <row r="152" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A152" s="145">
         <v>7651</v>
       </c>
@@ -13563,7 +13563,7 @@
       <c r="BN152" s="122"/>
       <c r="BO152" s="122"/>
     </row>
-    <row r="153" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="48" t="s">
         <v>104</v>
       </c>
@@ -13636,7 +13636,7 @@
       <c r="BN153" s="122"/>
       <c r="BO153" s="122"/>
     </row>
-    <row r="154" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A154" s="145">
         <v>7485</v>
       </c>
@@ -13724,7 +13724,7 @@
       <c r="BN154" s="122"/>
       <c r="BO154" s="122"/>
     </row>
-    <row r="155" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="48" t="s">
         <v>104</v>
       </c>
@@ -13741,7 +13741,7 @@
       <c r="J155" s="44"/>
       <c r="L155" s="122"/>
     </row>
-    <row r="156" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A156" s="58">
         <v>6620</v>
       </c>
@@ -13771,7 +13771,7 @@
       <c r="J156" s="29"/>
       <c r="L156" s="122"/>
     </row>
-    <row r="157" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="58">
         <v>7187</v>
       </c>
@@ -13801,7 +13801,7 @@
       <c r="J157" s="29"/>
       <c r="L157" s="122"/>
     </row>
-    <row r="158" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="145">
         <v>6008</v>
       </c>
@@ -13833,7 +13833,7 @@
       </c>
       <c r="L158" s="122"/>
     </row>
-    <row r="159" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="58">
         <v>7090</v>
       </c>
@@ -13863,7 +13863,7 @@
       <c r="J159" s="29"/>
       <c r="L159" s="122"/>
     </row>
-    <row r="160" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="58">
         <v>7103</v>
       </c>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="L161" s="122"/>
     </row>
-    <row r="162" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="58">
         <v>7092</v>
       </c>
@@ -13957,7 +13957,7 @@
       <c r="J162" s="29"/>
       <c r="L162" s="122"/>
     </row>
-    <row r="163" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="58">
         <v>6448</v>
       </c>
@@ -13987,7 +13987,7 @@
       <c r="J163" s="29"/>
       <c r="L163" s="122"/>
     </row>
-    <row r="164" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="58">
         <v>6754</v>
       </c>
@@ -14017,7 +14017,7 @@
       <c r="J164" s="29"/>
       <c r="L164" s="122"/>
     </row>
-    <row r="165" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="58">
         <v>6208</v>
       </c>
@@ -14047,7 +14047,7 @@
       <c r="J165" s="29"/>
       <c r="L165" s="122"/>
     </row>
-    <row r="166" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="58">
         <v>6228</v>
       </c>
@@ -29376,6 +29376,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A9:J168" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:J167">
       <sortCondition ref="A9:A168"/>
     </sortState>
